--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="17426"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\InputData\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="80" windowWidth="23000" windowHeight="11580" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>RM Reserve Margin</t>
   </si>
@@ -46,25 +46,27 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>The reserve margin in the U.S. dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support</t>
-  </si>
-  <si>
-    <t>countries that project changes in future reserve margin by year.</t>
-  </si>
-  <si>
-    <t>use China variables</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t xml:space="preserve">The reserve margin (difference between the total generation available and the forecasted peak demand) in the U.S. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support countries that project </t>
+  </si>
+  <si>
+    <t>changes in future reserve margin by year.</t>
+  </si>
+  <si>
+    <t>(dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -72,23 +74,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -112,19 +99,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -140,7 +124,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -215,23 +199,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -267,23 +234,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -460,18 +410,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -479,48 +426,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -532,276 +478,269 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1">
         <v>2015</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1">
         <v>2016</v>
       </c>
-      <c r="D1" s="4">
+      <c r="D1">
         <v>2017</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>2018</v>
       </c>
-      <c r="F1" s="4">
+      <c r="F1">
         <v>2019</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1">
         <v>2020</v>
       </c>
-      <c r="H1" s="4">
+      <c r="H1">
         <v>2021</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1">
         <v>2022</v>
       </c>
-      <c r="J1" s="4">
+      <c r="J1">
         <v>2023</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1">
         <v>2024</v>
       </c>
-      <c r="L1" s="4">
+      <c r="L1">
         <v>2025</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1">
         <v>2026</v>
       </c>
-      <c r="N1" s="4">
+      <c r="N1">
         <v>2027</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1">
         <v>2028</v>
       </c>
-      <c r="P1" s="4">
+      <c r="P1">
         <v>2029</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1">
         <v>2030</v>
       </c>
-      <c r="R1" s="4">
+      <c r="R1">
         <v>2031</v>
       </c>
-      <c r="S1" s="4">
+      <c r="S1">
         <v>2032</v>
       </c>
-      <c r="T1" s="4">
+      <c r="T1">
         <v>2033</v>
       </c>
-      <c r="U1" s="4">
+      <c r="U1">
         <v>2034</v>
       </c>
-      <c r="V1" s="4">
+      <c r="V1">
         <v>2035</v>
       </c>
-      <c r="W1" s="4">
+      <c r="W1">
         <v>2036</v>
       </c>
-      <c r="X1" s="4">
+      <c r="X1">
         <v>2037</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Y1">
         <v>2038</v>
       </c>
-      <c r="Z1" s="4">
+      <c r="Z1">
         <v>2039</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AA1">
         <v>2040</v>
       </c>
-      <c r="AB1" s="4">
+      <c r="AB1">
         <v>2041</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AC1">
         <v>2042</v>
       </c>
-      <c r="AD1" s="4">
+      <c r="AD1">
         <v>2043</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AE1">
         <v>2044</v>
       </c>
-      <c r="AF1" s="4">
+      <c r="AF1">
         <v>2045</v>
       </c>
-      <c r="AG1" s="4">
+      <c r="AG1">
         <v>2046</v>
       </c>
-      <c r="AH1" s="4">
+      <c r="AH1">
         <v>2047</v>
       </c>
-      <c r="AI1" s="4">
+      <c r="AI1">
         <v>2048</v>
       </c>
-      <c r="AJ1" s="4">
+      <c r="AJ1">
         <v>2049</v>
       </c>
-      <c r="AK1" s="4">
+      <c r="AK1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="N2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="S2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="T2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="V2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="W2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="X2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AC2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AD2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AE2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AF2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AG2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AH2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AI2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AJ2" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="AK2" s="4">
-        <v>0.15</v>
+      <c r="B2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>0.14119999999999999</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -809,24 +748,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -845,70 +845,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1010,33 +963,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E0CDF1-7B82-4293-99A8-2CFCDCA1CB2B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCBE8159-A2B8-4A5E-A790-1347142ACA6C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F591111-B7DD-44B4-A52D-412B1B6B88F5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316E2D11-2D5C-42C3-93B4-77C11D2193AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2961696A-7B31-4E95-A2BA-19B0908E8DCF}"/>
 </file>